--- a/0402代办-AI赋能运营内容封面.xlsx
+++ b/0402代办-AI赋能运营内容封面.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10517"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10525"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/a1234/Desktop/ai/poster/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17E3C3BE-3013-DA44-A805-F92EEFF1B87C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CEF8C8FB-C6AF-BE4F-B751-5538BB20B39F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2200" yWindow="660" windowWidth="28040" windowHeight="15800" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,16 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="31">
-  <si>
-    <t>一级标签</t>
-  </si>
-  <si>
-    <t>二级标签</t>
-  </si>
-  <si>
-    <t>三级标签</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="31">
   <si>
     <t>教育动态</t>
   </si>
@@ -46,12 +37,6 @@
   </si>
   <si>
     <t>学科同步</t>
-  </si>
-  <si>
-    <t>标题</t>
-  </si>
-  <si>
-    <t>老师图</t>
   </si>
   <si>
     <t>升学新政</t>
@@ -118,6 +103,26 @@
   </si>
   <si>
     <t>色彩心理学</t>
+  </si>
+  <si>
+    <t>一级标签</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>二级标签</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>三级标签</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>标题</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>老师图</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -318,7 +323,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -347,9 +352,6 @@
     <xf numFmtId="0" fontId="2" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -369,182 +371,6 @@
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>38100</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>38100</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>-38100</xdr:colOff>
-      <xdr:row>3</xdr:row>
-      <xdr:rowOff>-38100</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Picture 2" descr="XSVoma">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0300-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>38100</xdr:colOff>
-      <xdr:row>13</xdr:row>
-      <xdr:rowOff>38100</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>-38100</xdr:colOff>
-      <xdr:row>14</xdr:row>
-      <xdr:rowOff>-38100</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="Picture 3" descr="gkULDV">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0300-000003000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>38100</xdr:colOff>
-      <xdr:row>12</xdr:row>
-      <xdr:rowOff>38100</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>-38100</xdr:colOff>
-      <xdr:row>13</xdr:row>
-      <xdr:rowOff>-38100</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="4" name="Picture 4" descr="zfCtgo">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0300-000004000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>38100</xdr:colOff>
-      <xdr:row>9</xdr:row>
-      <xdr:rowOff>38100</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>-38100</xdr:colOff>
-      <xdr:row>10</xdr:row>
-      <xdr:rowOff>-38100</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="5" name="Picture 5" descr="FvDvle">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0300-000005000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>4</xdr:col>
@@ -572,95 +398,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>38100</xdr:colOff>
-      <xdr:row>11</xdr:row>
-      <xdr:rowOff>38100</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>-38100</xdr:colOff>
-      <xdr:row>12</xdr:row>
-      <xdr:rowOff>-38100</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="7" name="Picture 7" descr="lxoLDb">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0300-000007000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>38100</xdr:colOff>
-      <xdr:row>10</xdr:row>
-      <xdr:rowOff>38100</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>-38100</xdr:colOff>
-      <xdr:row>11</xdr:row>
-      <xdr:rowOff>-38100</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="8" name="Picture 8" descr="PdUSod">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0300-000008000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -704,95 +442,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>38100</xdr:colOff>
-      <xdr:row>4</xdr:row>
-      <xdr:rowOff>38100</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>-38100</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>-38100</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="10" name="Picture 10" descr="RBWDOC">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0300-00000A000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>38100</xdr:colOff>
-      <xdr:row>7</xdr:row>
-      <xdr:rowOff>38100</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>-38100</xdr:colOff>
-      <xdr:row>8</xdr:row>
-      <xdr:rowOff>-38100</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="11" name="Picture 11" descr="hrgnZu">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0300-00000B000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId10"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -836,7 +486,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId11"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -880,51 +530,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId12"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>38100</xdr:colOff>
-      <xdr:row>3</xdr:row>
-      <xdr:rowOff>38100</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>-38100</xdr:colOff>
-      <xdr:row>4</xdr:row>
-      <xdr:rowOff>-38100</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="14" name="Picture 14" descr="qhKICv">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0300-00000E000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId13"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1255,19 +861,19 @@
   <sheetData>
     <row r="1" spans="1:18" ht="15">
       <c r="A1" s="3" t="s">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>1</v>
+        <v>27</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>2</v>
+        <v>28</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>7</v>
+        <v>29</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="F1" s="8"/>
       <c r="G1" s="8"/>
@@ -1284,17 +890,17 @@
       <c r="R1" s="8"/>
     </row>
     <row r="2" spans="1:18" ht="114.5" customHeight="1">
-      <c r="A2" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" s="10" t="s">
+      <c r="A2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="1" t="s">
-        <v>9</v>
-      </c>
       <c r="D2" s="7" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E2" s="6"/>
       <c r="F2" s="8"/>
@@ -1312,13 +918,17 @@
       <c r="R2" s="8"/>
     </row>
     <row r="3" spans="1:18" ht="97.25" customHeight="1">
-      <c r="A3" s="10"/>
-      <c r="B3" s="10"/>
+      <c r="A3" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>1</v>
+      </c>
       <c r="C3" s="1" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="E3" s="6"/>
       <c r="F3" s="8"/>
@@ -1336,17 +946,17 @@
       <c r="R3" s="8"/>
     </row>
     <row r="4" spans="1:18" ht="80.25" customHeight="1">
-      <c r="A4" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="B4" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="C4" s="10" t="s">
-        <v>13</v>
+      <c r="A4" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>8</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E4" s="6"/>
       <c r="F4" s="8"/>
@@ -1364,11 +974,17 @@
       <c r="R4" s="8"/>
     </row>
     <row r="5" spans="1:18" ht="136.5" customHeight="1">
-      <c r="A5" s="10"/>
-      <c r="B5" s="10"/>
-      <c r="C5" s="10"/>
+      <c r="A5" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>8</v>
+      </c>
       <c r="D5" s="5" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E5" s="6"/>
       <c r="F5" s="8"/>
@@ -1386,13 +1002,17 @@
       <c r="R5" s="8"/>
     </row>
     <row r="6" spans="1:18" ht="135" customHeight="1">
-      <c r="A6" s="10"/>
-      <c r="B6" s="10"/>
-      <c r="C6" s="10" t="s">
-        <v>16</v>
+      <c r="A6" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>11</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="E6" s="6"/>
       <c r="F6" s="8"/>
@@ -1410,11 +1030,17 @@
       <c r="R6" s="8"/>
     </row>
     <row r="7" spans="1:18" ht="141.5" customHeight="1">
-      <c r="A7" s="10"/>
-      <c r="B7" s="10"/>
-      <c r="C7" s="10"/>
+      <c r="A7" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>11</v>
+      </c>
       <c r="D7" s="5" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="E7" s="6"/>
       <c r="F7" s="8"/>
@@ -1432,13 +1058,17 @@
       <c r="R7" s="8"/>
     </row>
     <row r="8" spans="1:18" ht="123.25" customHeight="1">
-      <c r="A8" s="10"/>
-      <c r="B8" s="10"/>
-      <c r="C8" s="10" t="s">
-        <v>19</v>
+      <c r="A8" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>14</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="E8" s="6"/>
       <c r="F8" s="8"/>
@@ -1456,11 +1086,17 @@
       <c r="R8" s="8"/>
     </row>
     <row r="9" spans="1:18" ht="119.5" customHeight="1">
-      <c r="A9" s="10"/>
-      <c r="B9" s="10"/>
-      <c r="C9" s="10"/>
+      <c r="A9" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>14</v>
+      </c>
       <c r="D9" s="4" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="E9" s="6"/>
       <c r="F9" s="8"/>
@@ -1478,13 +1114,17 @@
       <c r="R9" s="8"/>
     </row>
     <row r="10" spans="1:18" ht="86.25" customHeight="1">
-      <c r="A10" s="10"/>
-      <c r="B10" s="10"/>
+      <c r="A10" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>3</v>
+      </c>
       <c r="C10" s="1" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="E10" s="6"/>
       <c r="F10" s="8"/>
@@ -1502,13 +1142,17 @@
       <c r="R10" s="8"/>
     </row>
     <row r="11" spans="1:18" ht="78.25" customHeight="1">
-      <c r="A11" s="10"/>
-      <c r="B11" s="10"/>
+      <c r="A11" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>3</v>
+      </c>
       <c r="C11" s="1" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="E11" s="6"/>
       <c r="F11" s="8"/>
@@ -1526,13 +1170,17 @@
       <c r="R11" s="8"/>
     </row>
     <row r="12" spans="1:18" ht="136.5" customHeight="1">
-      <c r="A12" s="10"/>
-      <c r="B12" s="10"/>
+      <c r="A12" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>3</v>
+      </c>
       <c r="C12" s="1" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="D12" s="9" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="E12" s="6"/>
       <c r="F12" s="8"/>
@@ -1550,13 +1198,17 @@
       <c r="R12" s="8"/>
     </row>
     <row r="13" spans="1:18" ht="95.5" customHeight="1">
-      <c r="A13" s="10"/>
-      <c r="B13" s="10"/>
-      <c r="C13" s="10" t="s">
-        <v>28</v>
+      <c r="A13" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="E13" s="6"/>
       <c r="F13" s="8"/>
@@ -1574,11 +1226,17 @@
       <c r="R13" s="8"/>
     </row>
     <row r="14" spans="1:18" ht="119.25" customHeight="1">
-      <c r="A14" s="10"/>
-      <c r="B14" s="10"/>
-      <c r="C14" s="10"/>
+      <c r="A14" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>23</v>
+      </c>
       <c r="D14" s="7" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="E14" s="6"/>
       <c r="F14" s="8"/>
@@ -5316,16 +4974,6 @@
       <c r="R200" s="8"/>
     </row>
   </sheetData>
-  <mergeCells count="8">
-    <mergeCell ref="A4:A14"/>
-    <mergeCell ref="B2:B3"/>
-    <mergeCell ref="A2:A3"/>
-    <mergeCell ref="C13:C14"/>
-    <mergeCell ref="C8:C9"/>
-    <mergeCell ref="C6:C7"/>
-    <mergeCell ref="C4:C5"/>
-    <mergeCell ref="B4:B14"/>
-  </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
